--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ137"/>
+  <dimension ref="A1:AZ148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,48 +986,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119599068</v>
+        <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>90659</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1593</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gärdselet, Gärdselet, Ång</t>
+          <t>Löningsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600097</v>
+        <v>600299</v>
       </c>
       <c r="R5" t="n">
-        <v>7064135</v>
+        <v>7063902</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,17 +1051,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Angenämt kryddoftande</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,65 +1081,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599068</t>
+          <t>https://artportalen.se/Sighting/137099440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119699628</v>
+        <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>90659</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1593</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gärdselet, Gärdselet, Ång</t>
+          <t>Löningsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600079</v>
+        <v>600362</v>
       </c>
       <c r="R6" t="n">
-        <v>7064155</v>
+        <v>7063815</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,12 +1163,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,24 +1193,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119699628</t>
+          <t>https://artportalen.se/Sighting/137099819</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119700183</v>
+        <v>119599068</v>
       </c>
       <c r="B7" t="n">
         <v>90659</v>
@@ -1230,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600112</v>
+        <v>600097</v>
       </c>
       <c r="R7" t="n">
-        <v>7064120</v>
+        <v>7064135</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1260,12 +1275,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Angenämt kryddoftande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,16 +1311,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700183</t>
+          <t>https://artportalen.se/Sighting/119599068</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119602978</v>
+        <v>119699628</v>
       </c>
       <c r="B8" t="n">
-        <v>90674</v>
+        <v>90659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600027</v>
+        <v>600079</v>
       </c>
       <c r="R8" t="n">
-        <v>7063859</v>
+        <v>7064155</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,12 +1382,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,16 +1413,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119602978</t>
+          <t>https://artportalen.se/Sighting/119699628</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119597287</v>
+        <v>119700183</v>
       </c>
       <c r="B9" t="n">
-        <v>92692</v>
+        <v>90659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,40 +1430,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1958</v>
+        <v>1593</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gärdselet, Gärdselet, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600073</v>
+        <v>600112</v>
       </c>
       <c r="R9" t="n">
-        <v>7064052</v>
+        <v>7064120</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1467,17 +1484,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Lammticka? Sandtallskog</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,7 +1498,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1504,16 +1515,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119597287</t>
+          <t>https://artportalen.se/Sighting/119700183</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119699204</v>
+        <v>119602978</v>
       </c>
       <c r="B10" t="n">
-        <v>92692</v>
+        <v>90674</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1958</v>
+        <v>1596</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,13 +1556,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600071</v>
+        <v>600027</v>
       </c>
       <c r="R10" t="n">
-        <v>7064047</v>
+        <v>7063859</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1575,17 +1586,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lammticka? Sandtallskog</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,16 +1617,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119699204</t>
+          <t>https://artportalen.se/Sighting/119602978</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119597817</v>
+        <v>119597287</v>
       </c>
       <c r="B11" t="n">
-        <v>93213</v>
+        <v>92692</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,34 +1634,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>1958</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gärdselet, Gärdselet, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600059</v>
+        <v>600073</v>
       </c>
       <c r="R11" t="n">
-        <v>7064091</v>
+        <v>7064052</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,12 +1699,18 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lammticka? Sandtallskog</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1713,16 +1728,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119597817</t>
+          <t>https://artportalen.se/Sighting/119597287</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119600257</v>
+        <v>119699204</v>
       </c>
       <c r="B12" t="n">
-        <v>93213</v>
+        <v>92692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1745,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>1958</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,13 +1769,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600262</v>
+        <v>600071</v>
       </c>
       <c r="R12" t="n">
-        <v>7064001</v>
+        <v>7064047</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1784,12 +1799,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lammticka? Sandtallskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1815,13 +1835,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119600257</t>
+          <t>https://artportalen.se/Sighting/119699204</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119600718</v>
+        <v>119597817</v>
       </c>
       <c r="B13" t="n">
         <v>93213</v>
@@ -1856,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600160</v>
+        <v>600059</v>
       </c>
       <c r="R13" t="n">
-        <v>7063973</v>
+        <v>7064091</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,13 +1937,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119600718</t>
+          <t>https://artportalen.se/Sighting/119597817</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119601615</v>
+        <v>119600257</v>
       </c>
       <c r="B14" t="n">
         <v>93213</v>
@@ -1958,13 +1978,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600021</v>
+        <v>600262</v>
       </c>
       <c r="R14" t="n">
-        <v>7063997</v>
+        <v>7064001</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2019,13 +2039,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119601615</t>
+          <t>https://artportalen.se/Sighting/119600257</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119602216</v>
+        <v>119600718</v>
       </c>
       <c r="B15" t="n">
         <v>93213</v>
@@ -2060,13 +2080,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600023</v>
+        <v>600160</v>
       </c>
       <c r="R15" t="n">
-        <v>7063947</v>
+        <v>7063973</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2121,13 +2141,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119602216</t>
+          <t>https://artportalen.se/Sighting/119600718</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119603845</v>
+        <v>119601615</v>
       </c>
       <c r="B16" t="n">
         <v>93213</v>
@@ -2162,13 +2182,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600111</v>
+        <v>600021</v>
       </c>
       <c r="R16" t="n">
-        <v>7063808</v>
+        <v>7063997</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2223,13 +2243,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603845</t>
+          <t>https://artportalen.se/Sighting/119601615</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119603970</v>
+        <v>119602216</v>
       </c>
       <c r="B17" t="n">
         <v>93213</v>
@@ -2264,13 +2284,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600127</v>
+        <v>600023</v>
       </c>
       <c r="R17" t="n">
-        <v>7063820</v>
+        <v>7063947</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2325,13 +2345,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603970</t>
+          <t>https://artportalen.se/Sighting/119602216</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119700233</v>
+        <v>119603845</v>
       </c>
       <c r="B18" t="n">
         <v>93213</v>
@@ -2366,13 +2386,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600083</v>
+        <v>600111</v>
       </c>
       <c r="R18" t="n">
-        <v>7064124</v>
+        <v>7063808</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2396,12 +2416,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,13 +2447,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700233</t>
+          <t>https://artportalen.se/Sighting/119603845</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119700659</v>
+        <v>119603970</v>
       </c>
       <c r="B19" t="n">
         <v>93213</v>
@@ -2468,10 +2488,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600147</v>
+        <v>600127</v>
       </c>
       <c r="R19" t="n">
-        <v>7064015</v>
+        <v>7063820</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,12 +2518,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2529,13 +2549,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700659</t>
+          <t>https://artportalen.se/Sighting/119603970</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119700720</v>
+        <v>119700233</v>
       </c>
       <c r="B20" t="n">
         <v>93213</v>
@@ -2570,13 +2590,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600154</v>
+        <v>600083</v>
       </c>
       <c r="R20" t="n">
-        <v>7064003</v>
+        <v>7064124</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2631,38 +2651,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700720</t>
+          <t>https://artportalen.se/Sighting/119700233</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119598208</v>
+        <v>119700659</v>
       </c>
       <c r="B21" t="n">
-        <v>93189</v>
+        <v>93213</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2672,10 +2692,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600105</v>
+        <v>600147</v>
       </c>
       <c r="R21" t="n">
-        <v>7064110</v>
+        <v>7064015</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,12 +2722,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2733,38 +2753,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119598208</t>
+          <t>https://artportalen.se/Sighting/119700659</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119599097</v>
+        <v>119700720</v>
       </c>
       <c r="B22" t="n">
-        <v>93189</v>
+        <v>93213</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2774,10 +2794,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600088</v>
+        <v>600154</v>
       </c>
       <c r="R22" t="n">
-        <v>7064151</v>
+        <v>7064003</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2804,12 +2824,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,13 +2855,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599097</t>
+          <t>https://artportalen.se/Sighting/119700720</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119600313</v>
+        <v>119598208</v>
       </c>
       <c r="B23" t="n">
         <v>93189</v>
@@ -2876,10 +2896,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600265</v>
+        <v>600105</v>
       </c>
       <c r="R23" t="n">
-        <v>7064003</v>
+        <v>7064110</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,13 +2957,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119600313</t>
+          <t>https://artportalen.se/Sighting/119598208</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119600989</v>
+        <v>119599097</v>
       </c>
       <c r="B24" t="n">
         <v>93189</v>
@@ -2978,13 +2998,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600043</v>
+        <v>600088</v>
       </c>
       <c r="R24" t="n">
-        <v>7064026</v>
+        <v>7064151</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3039,13 +3059,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119600989</t>
+          <t>https://artportalen.se/Sighting/119599097</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119601978</v>
+        <v>119600313</v>
       </c>
       <c r="B25" t="n">
         <v>93189</v>
@@ -3080,13 +3100,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600023</v>
+        <v>600265</v>
       </c>
       <c r="R25" t="n">
-        <v>7063987</v>
+        <v>7064003</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3141,13 +3161,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119601978</t>
+          <t>https://artportalen.se/Sighting/119600313</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119602430</v>
+        <v>119600989</v>
       </c>
       <c r="B26" t="n">
         <v>93189</v>
@@ -3182,13 +3202,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600009</v>
+        <v>600043</v>
       </c>
       <c r="R26" t="n">
-        <v>7063942</v>
+        <v>7064026</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3243,13 +3263,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119602430</t>
+          <t>https://artportalen.se/Sighting/119600989</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119602491</v>
+        <v>119601978</v>
       </c>
       <c r="B27" t="n">
         <v>93189</v>
@@ -3284,13 +3304,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599988</v>
+        <v>600023</v>
       </c>
       <c r="R27" t="n">
-        <v>7063932</v>
+        <v>7063987</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3345,13 +3365,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119602491</t>
+          <t>https://artportalen.se/Sighting/119601978</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119602612</v>
+        <v>119602430</v>
       </c>
       <c r="B28" t="n">
         <v>93189</v>
@@ -3386,13 +3406,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600012</v>
+        <v>600009</v>
       </c>
       <c r="R28" t="n">
-        <v>7063895</v>
+        <v>7063942</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3447,13 +3467,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119602612</t>
+          <t>https://artportalen.se/Sighting/119602430</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119603076</v>
+        <v>119602491</v>
       </c>
       <c r="B29" t="n">
         <v>93189</v>
@@ -3488,10 +3508,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>600047</v>
+        <v>599988</v>
       </c>
       <c r="R29" t="n">
-        <v>7063848</v>
+        <v>7063932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3549,13 +3569,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603076</t>
+          <t>https://artportalen.se/Sighting/119602491</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119603242</v>
+        <v>119602612</v>
       </c>
       <c r="B30" t="n">
         <v>93189</v>
@@ -3590,10 +3610,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>600075</v>
+        <v>600012</v>
       </c>
       <c r="R30" t="n">
-        <v>7063871</v>
+        <v>7063895</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,13 +3671,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603242</t>
+          <t>https://artportalen.se/Sighting/119602612</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119603634</v>
+        <v>119603076</v>
       </c>
       <c r="B31" t="n">
         <v>93189</v>
@@ -3692,13 +3712,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>600099</v>
+        <v>600047</v>
       </c>
       <c r="R31" t="n">
-        <v>7063847</v>
+        <v>7063848</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3753,13 +3773,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603634</t>
+          <t>https://artportalen.se/Sighting/119603076</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119603730</v>
+        <v>119603242</v>
       </c>
       <c r="B32" t="n">
         <v>93189</v>
@@ -3794,13 +3814,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>600099</v>
+        <v>600075</v>
       </c>
       <c r="R32" t="n">
-        <v>7063822</v>
+        <v>7063871</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3855,13 +3875,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603730</t>
+          <t>https://artportalen.se/Sighting/119603242</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119603810</v>
+        <v>119603634</v>
       </c>
       <c r="B33" t="n">
         <v>93189</v>
@@ -3896,13 +3916,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>600098</v>
+        <v>600099</v>
       </c>
       <c r="R33" t="n">
-        <v>7063823</v>
+        <v>7063847</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3957,13 +3977,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603810</t>
+          <t>https://artportalen.se/Sighting/119603634</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119603986</v>
+        <v>119603730</v>
       </c>
       <c r="B34" t="n">
         <v>93189</v>
@@ -3998,13 +4018,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>600138</v>
+        <v>600099</v>
       </c>
       <c r="R34" t="n">
-        <v>7063796</v>
+        <v>7063822</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4059,13 +4079,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603986</t>
+          <t>https://artportalen.se/Sighting/119603730</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119626349</v>
+        <v>119603810</v>
       </c>
       <c r="B35" t="n">
         <v>93189</v>
@@ -4100,13 +4120,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>600061</v>
+        <v>600098</v>
       </c>
       <c r="R35" t="n">
-        <v>7063967</v>
+        <v>7063823</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4130,12 +4150,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4161,13 +4181,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119626349</t>
+          <t>https://artportalen.se/Sighting/119603810</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119626380</v>
+        <v>119603986</v>
       </c>
       <c r="B36" t="n">
         <v>93189</v>
@@ -4202,13 +4222,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>600053</v>
+        <v>600138</v>
       </c>
       <c r="R36" t="n">
-        <v>7063953</v>
+        <v>7063796</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4232,12 +4252,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4263,13 +4283,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119626380</t>
+          <t>https://artportalen.se/Sighting/119603986</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119626760</v>
+        <v>119626349</v>
       </c>
       <c r="B37" t="n">
         <v>93189</v>
@@ -4304,10 +4324,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>600030</v>
+        <v>600061</v>
       </c>
       <c r="R37" t="n">
-        <v>7063902</v>
+        <v>7063967</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4365,13 +4385,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119626760</t>
+          <t>https://artportalen.se/Sighting/119626349</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119698878</v>
+        <v>119626380</v>
       </c>
       <c r="B38" t="n">
         <v>93189</v>
@@ -4406,13 +4426,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>600039</v>
+        <v>600053</v>
       </c>
       <c r="R38" t="n">
-        <v>7064066</v>
+        <v>7063953</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4436,12 +4456,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4467,13 +4487,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119698878</t>
+          <t>https://artportalen.se/Sighting/119626380</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119699392</v>
+        <v>119626760</v>
       </c>
       <c r="B39" t="n">
         <v>93189</v>
@@ -4508,13 +4528,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>600077</v>
+        <v>600030</v>
       </c>
       <c r="R39" t="n">
-        <v>7064088</v>
+        <v>7063902</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4538,12 +4558,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4569,13 +4589,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119699392</t>
+          <t>https://artportalen.se/Sighting/119626760</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119699732</v>
+        <v>119698878</v>
       </c>
       <c r="B40" t="n">
         <v>93189</v>
@@ -4610,13 +4630,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>600074</v>
+        <v>600039</v>
       </c>
       <c r="R40" t="n">
-        <v>7064233</v>
+        <v>7064066</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4671,13 +4691,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119699732</t>
+          <t>https://artportalen.se/Sighting/119698878</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119699880</v>
+        <v>119699392</v>
       </c>
       <c r="B41" t="n">
         <v>93189</v>
@@ -4712,10 +4732,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>600094</v>
+        <v>600077</v>
       </c>
       <c r="R41" t="n">
-        <v>7064208</v>
+        <v>7064088</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4773,16 +4793,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119699880</t>
+          <t>https://artportalen.se/Sighting/119699392</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119598440</v>
+        <v>119699732</v>
       </c>
       <c r="B42" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4790,21 +4810,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4814,10 +4834,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>600092</v>
+        <v>600074</v>
       </c>
       <c r="R42" t="n">
-        <v>7064127</v>
+        <v>7064233</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4844,12 +4864,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4875,16 +4895,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119598440</t>
+          <t>https://artportalen.se/Sighting/119699732</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119599627</v>
+        <v>119699880</v>
       </c>
       <c r="B43" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4892,21 +4912,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4916,13 +4936,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>600134</v>
+        <v>600094</v>
       </c>
       <c r="R43" t="n">
-        <v>7064052</v>
+        <v>7064208</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4946,12 +4966,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4977,13 +4997,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599627</t>
+          <t>https://artportalen.se/Sighting/119699880</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119599792</v>
+        <v>119598440</v>
       </c>
       <c r="B44" t="n">
         <v>93191</v>
@@ -5018,10 +5038,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>600141</v>
+        <v>600092</v>
       </c>
       <c r="R44" t="n">
-        <v>7064045</v>
+        <v>7064127</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5079,13 +5099,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599792</t>
+          <t>https://artportalen.se/Sighting/119598440</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119600087</v>
+        <v>119599627</v>
       </c>
       <c r="B45" t="n">
         <v>93191</v>
@@ -5120,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>600225</v>
+        <v>600134</v>
       </c>
       <c r="R45" t="n">
-        <v>7063981</v>
+        <v>7064052</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5181,13 +5201,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119600087</t>
+          <t>https://artportalen.se/Sighting/119599627</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119600661</v>
+        <v>119599792</v>
       </c>
       <c r="B46" t="n">
         <v>93191</v>
@@ -5222,13 +5242,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>600169</v>
+        <v>600141</v>
       </c>
       <c r="R46" t="n">
-        <v>7063974</v>
+        <v>7064045</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5283,13 +5303,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119600661</t>
+          <t>https://artportalen.se/Sighting/119599792</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119600910</v>
+        <v>119600087</v>
       </c>
       <c r="B47" t="n">
         <v>93191</v>
@@ -5324,13 +5344,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>600095</v>
+        <v>600225</v>
       </c>
       <c r="R47" t="n">
-        <v>7063998</v>
+        <v>7063981</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5385,13 +5405,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119600910</t>
+          <t>https://artportalen.se/Sighting/119600087</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119625722</v>
+        <v>119600661</v>
       </c>
       <c r="B48" t="n">
         <v>93191</v>
@@ -5426,10 +5446,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>600130</v>
+        <v>600169</v>
       </c>
       <c r="R48" t="n">
-        <v>7063966</v>
+        <v>7063974</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5456,12 +5476,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5487,13 +5507,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625722</t>
+          <t>https://artportalen.se/Sighting/119600661</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119626010</v>
+        <v>119600910</v>
       </c>
       <c r="B49" t="n">
         <v>93191</v>
@@ -5528,13 +5548,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>600084</v>
+        <v>600095</v>
       </c>
       <c r="R49" t="n">
-        <v>7064000</v>
+        <v>7063998</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5558,12 +5578,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5589,13 +5609,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119626010</t>
+          <t>https://artportalen.se/Sighting/119600910</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119626559</v>
+        <v>119625722</v>
       </c>
       <c r="B50" t="n">
         <v>93191</v>
@@ -5630,13 +5650,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>600056</v>
+        <v>600130</v>
       </c>
       <c r="R50" t="n">
-        <v>7063938</v>
+        <v>7063966</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5691,13 +5711,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119626559</t>
+          <t>https://artportalen.se/Sighting/119625722</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119626958</v>
+        <v>119626010</v>
       </c>
       <c r="B51" t="n">
         <v>93191</v>
@@ -5732,10 +5752,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>600137</v>
+        <v>600084</v>
       </c>
       <c r="R51" t="n">
-        <v>7063925</v>
+        <v>7064000</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5793,13 +5813,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119626958</t>
+          <t>https://artportalen.se/Sighting/119626010</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119700612</v>
+        <v>119626559</v>
       </c>
       <c r="B52" t="n">
         <v>93191</v>
@@ -5834,10 +5854,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>600142</v>
+        <v>600056</v>
       </c>
       <c r="R52" t="n">
-        <v>7064031</v>
+        <v>7063938</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5864,12 +5884,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5895,16 +5915,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700612</t>
+          <t>https://artportalen.se/Sighting/119626559</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119597460</v>
+        <v>119626958</v>
       </c>
       <c r="B53" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5912,21 +5932,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5936,13 +5956,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>600063</v>
+        <v>600137</v>
       </c>
       <c r="R53" t="n">
-        <v>7064034</v>
+        <v>7063925</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5966,12 +5986,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5997,16 +6017,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119597460</t>
+          <t>https://artportalen.se/Sighting/119626958</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119597623</v>
+        <v>119700612</v>
       </c>
       <c r="B54" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6014,21 +6034,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6038,10 +6058,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>600056</v>
+        <v>600142</v>
       </c>
       <c r="R54" t="n">
-        <v>7064069</v>
+        <v>7064031</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6068,12 +6088,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6099,13 +6119,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119597623</t>
+          <t>https://artportalen.se/Sighting/119700612</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119597731</v>
+        <v>119597460</v>
       </c>
       <c r="B55" t="n">
         <v>93197</v>
@@ -6140,13 +6160,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>600065</v>
+        <v>600063</v>
       </c>
       <c r="R55" t="n">
-        <v>7064065</v>
+        <v>7064034</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6201,13 +6221,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119597731</t>
+          <t>https://artportalen.se/Sighting/119597460</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119597840</v>
+        <v>119597623</v>
       </c>
       <c r="B56" t="n">
         <v>93197</v>
@@ -6242,10 +6262,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>600050</v>
+        <v>600056</v>
       </c>
       <c r="R56" t="n">
-        <v>7064098</v>
+        <v>7064069</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6303,13 +6323,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119597840</t>
+          <t>https://artportalen.se/Sighting/119597623</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119598252</v>
+        <v>119597731</v>
       </c>
       <c r="B57" t="n">
         <v>93197</v>
@@ -6344,10 +6364,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>600099</v>
+        <v>600065</v>
       </c>
       <c r="R57" t="n">
-        <v>7064107</v>
+        <v>7064065</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6405,13 +6425,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119598252</t>
+          <t>https://artportalen.se/Sighting/119597731</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119598739</v>
+        <v>119597840</v>
       </c>
       <c r="B58" t="n">
         <v>93197</v>
@@ -6446,10 +6466,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>600088</v>
+        <v>600050</v>
       </c>
       <c r="R58" t="n">
-        <v>7064124</v>
+        <v>7064098</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6507,13 +6527,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119598739</t>
+          <t>https://artportalen.se/Sighting/119597840</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119599131</v>
+        <v>119598252</v>
       </c>
       <c r="B59" t="n">
         <v>93197</v>
@@ -6548,10 +6568,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>600090</v>
+        <v>600099</v>
       </c>
       <c r="R59" t="n">
-        <v>7064147</v>
+        <v>7064107</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6609,13 +6629,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599131</t>
+          <t>https://artportalen.se/Sighting/119598252</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119599365</v>
+        <v>119598739</v>
       </c>
       <c r="B60" t="n">
         <v>93197</v>
@@ -6650,13 +6670,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>600106</v>
+        <v>600088</v>
       </c>
       <c r="R60" t="n">
-        <v>7064158</v>
+        <v>7064124</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6711,13 +6731,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599365</t>
+          <t>https://artportalen.se/Sighting/119598739</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119599393</v>
+        <v>119599131</v>
       </c>
       <c r="B61" t="n">
         <v>93197</v>
@@ -6752,10 +6772,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>600121</v>
+        <v>600090</v>
       </c>
       <c r="R61" t="n">
-        <v>7064141</v>
+        <v>7064147</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6813,13 +6833,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599393</t>
+          <t>https://artportalen.se/Sighting/119599131</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119599449</v>
+        <v>119599365</v>
       </c>
       <c r="B62" t="n">
         <v>93197</v>
@@ -6854,13 +6874,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>600141</v>
+        <v>600106</v>
       </c>
       <c r="R62" t="n">
-        <v>7064106</v>
+        <v>7064158</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6915,13 +6935,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599449</t>
+          <t>https://artportalen.se/Sighting/119599365</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119599507</v>
+        <v>119599393</v>
       </c>
       <c r="B63" t="n">
         <v>93197</v>
@@ -6956,10 +6976,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>600101</v>
+        <v>600121</v>
       </c>
       <c r="R63" t="n">
-        <v>7064136</v>
+        <v>7064141</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7017,13 +7037,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599507</t>
+          <t>https://artportalen.se/Sighting/119599393</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119599651</v>
+        <v>119599449</v>
       </c>
       <c r="B64" t="n">
         <v>93197</v>
@@ -7058,10 +7078,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>600146</v>
+        <v>600141</v>
       </c>
       <c r="R64" t="n">
-        <v>7064060</v>
+        <v>7064106</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7119,13 +7139,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599651</t>
+          <t>https://artportalen.se/Sighting/119599449</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119599700</v>
+        <v>119599507</v>
       </c>
       <c r="B65" t="n">
         <v>93197</v>
@@ -7160,10 +7180,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>600161</v>
+        <v>600101</v>
       </c>
       <c r="R65" t="n">
-        <v>7064059</v>
+        <v>7064136</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7221,13 +7241,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599700</t>
+          <t>https://artportalen.se/Sighting/119599507</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119599734</v>
+        <v>119599651</v>
       </c>
       <c r="B66" t="n">
         <v>93197</v>
@@ -7262,10 +7282,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>600155</v>
+        <v>600146</v>
       </c>
       <c r="R66" t="n">
-        <v>7064029</v>
+        <v>7064060</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7323,13 +7343,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599734</t>
+          <t>https://artportalen.se/Sighting/119599651</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119599818</v>
+        <v>119599700</v>
       </c>
       <c r="B67" t="n">
         <v>93197</v>
@@ -7364,13 +7384,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>600170</v>
+        <v>600161</v>
       </c>
       <c r="R67" t="n">
-        <v>7063993</v>
+        <v>7064059</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7425,13 +7445,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599818</t>
+          <t>https://artportalen.se/Sighting/119599700</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119599847</v>
+        <v>119599734</v>
       </c>
       <c r="B68" t="n">
         <v>93197</v>
@@ -7466,13 +7486,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>600186</v>
+        <v>600155</v>
       </c>
       <c r="R68" t="n">
-        <v>7063984</v>
+        <v>7064029</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7527,13 +7547,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599847</t>
+          <t>https://artportalen.se/Sighting/119599734</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119600003</v>
+        <v>119599818</v>
       </c>
       <c r="B69" t="n">
         <v>93197</v>
@@ -7568,13 +7588,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>600201</v>
+        <v>600170</v>
       </c>
       <c r="R69" t="n">
-        <v>7063982</v>
+        <v>7063993</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7629,13 +7649,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119600003</t>
+          <t>https://artportalen.se/Sighting/119599818</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119600147</v>
+        <v>119599847</v>
       </c>
       <c r="B70" t="n">
         <v>93197</v>
@@ -7670,13 +7690,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>600259</v>
+        <v>600186</v>
       </c>
       <c r="R70" t="n">
-        <v>7063989</v>
+        <v>7063984</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7731,13 +7751,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119600147</t>
+          <t>https://artportalen.se/Sighting/119599847</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119600472</v>
+        <v>119600003</v>
       </c>
       <c r="B71" t="n">
         <v>93197</v>
@@ -7772,13 +7792,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>600237</v>
+        <v>600201</v>
       </c>
       <c r="R71" t="n">
-        <v>7064013</v>
+        <v>7063982</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7833,13 +7853,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119600472</t>
+          <t>https://artportalen.se/Sighting/119600003</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119600675</v>
+        <v>119600147</v>
       </c>
       <c r="B72" t="n">
         <v>93197</v>
@@ -7874,13 +7894,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>600177</v>
+        <v>600259</v>
       </c>
       <c r="R72" t="n">
-        <v>7063963</v>
+        <v>7063989</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7935,13 +7955,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119600675</t>
+          <t>https://artportalen.se/Sighting/119600147</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119600890</v>
+        <v>119600472</v>
       </c>
       <c r="B73" t="n">
         <v>93197</v>
@@ -7976,13 +7996,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>600095</v>
+        <v>600237</v>
       </c>
       <c r="R73" t="n">
-        <v>7064017</v>
+        <v>7064013</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8037,13 +8057,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119600890</t>
+          <t>https://artportalen.se/Sighting/119600472</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119602498</v>
+        <v>119600675</v>
       </c>
       <c r="B74" t="n">
         <v>93197</v>
@@ -8078,13 +8098,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>599983</v>
+        <v>600177</v>
       </c>
       <c r="R74" t="n">
-        <v>7063933</v>
+        <v>7063963</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8139,13 +8159,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119602498</t>
+          <t>https://artportalen.se/Sighting/119600675</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119603564</v>
+        <v>119600890</v>
       </c>
       <c r="B75" t="n">
         <v>93197</v>
@@ -8180,13 +8200,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>600094</v>
+        <v>600095</v>
       </c>
       <c r="R75" t="n">
-        <v>7063850</v>
+        <v>7064017</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8241,13 +8261,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603564</t>
+          <t>https://artportalen.se/Sighting/119600890</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119603741</v>
+        <v>119602498</v>
       </c>
       <c r="B76" t="n">
         <v>93197</v>
@@ -8282,13 +8302,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>600098</v>
+        <v>599983</v>
       </c>
       <c r="R76" t="n">
-        <v>7063824</v>
+        <v>7063933</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8343,13 +8363,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603741</t>
+          <t>https://artportalen.se/Sighting/119602498</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119603895</v>
+        <v>119603564</v>
       </c>
       <c r="B77" t="n">
         <v>93197</v>
@@ -8384,13 +8404,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>600116</v>
+        <v>600094</v>
       </c>
       <c r="R77" t="n">
-        <v>7063809</v>
+        <v>7063850</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8445,13 +8465,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603895</t>
+          <t>https://artportalen.se/Sighting/119603564</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119625755</v>
+        <v>119603741</v>
       </c>
       <c r="B78" t="n">
         <v>93197</v>
@@ -8486,13 +8506,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>600128</v>
+        <v>600098</v>
       </c>
       <c r="R78" t="n">
-        <v>7063972</v>
+        <v>7063824</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8516,12 +8536,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8547,13 +8567,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625755</t>
+          <t>https://artportalen.se/Sighting/119603741</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119625832</v>
+        <v>119603895</v>
       </c>
       <c r="B79" t="n">
         <v>93197</v>
@@ -8588,13 +8608,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>600078</v>
+        <v>600116</v>
       </c>
       <c r="R79" t="n">
-        <v>7063940</v>
+        <v>7063809</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8618,12 +8638,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8649,13 +8669,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625832</t>
+          <t>https://artportalen.se/Sighting/119603895</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119625864</v>
+        <v>119625755</v>
       </c>
       <c r="B80" t="n">
         <v>93197</v>
@@ -8690,10 +8710,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>600094</v>
+        <v>600128</v>
       </c>
       <c r="R80" t="n">
-        <v>7063943</v>
+        <v>7063972</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8751,13 +8771,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625864</t>
+          <t>https://artportalen.se/Sighting/119625755</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119625907</v>
+        <v>119625832</v>
       </c>
       <c r="B81" t="n">
         <v>93197</v>
@@ -8792,10 +8812,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>600080</v>
+        <v>600078</v>
       </c>
       <c r="R81" t="n">
-        <v>7063975</v>
+        <v>7063940</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8853,13 +8873,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625907</t>
+          <t>https://artportalen.se/Sighting/119625832</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119626067</v>
+        <v>119625864</v>
       </c>
       <c r="B82" t="n">
         <v>93197</v>
@@ -8894,13 +8914,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>600065</v>
+        <v>600094</v>
       </c>
       <c r="R82" t="n">
-        <v>7063996</v>
+        <v>7063943</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8955,13 +8975,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119626067</t>
+          <t>https://artportalen.se/Sighting/119625864</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119626156</v>
+        <v>119625907</v>
       </c>
       <c r="B83" t="n">
         <v>93197</v>
@@ -8996,10 +9016,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>600057</v>
+        <v>600080</v>
       </c>
       <c r="R83" t="n">
-        <v>7063976</v>
+        <v>7063975</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9057,13 +9077,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119626156</t>
+          <t>https://artportalen.se/Sighting/119625907</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119626366</v>
+        <v>119626067</v>
       </c>
       <c r="B84" t="n">
         <v>93197</v>
@@ -9098,13 +9118,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>600048</v>
+        <v>600065</v>
       </c>
       <c r="R84" t="n">
-        <v>7063947</v>
+        <v>7063996</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9159,13 +9179,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119626366</t>
+          <t>https://artportalen.se/Sighting/119626067</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119626794</v>
+        <v>119626156</v>
       </c>
       <c r="B85" t="n">
         <v>93197</v>
@@ -9200,10 +9220,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>600044</v>
+        <v>600057</v>
       </c>
       <c r="R85" t="n">
-        <v>7063902</v>
+        <v>7063976</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9261,13 +9281,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119626794</t>
+          <t>https://artportalen.se/Sighting/119626156</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119626854</v>
+        <v>119626366</v>
       </c>
       <c r="B86" t="n">
         <v>93197</v>
@@ -9302,13 +9322,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>600066</v>
+        <v>600048</v>
       </c>
       <c r="R86" t="n">
-        <v>7063913</v>
+        <v>7063947</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9363,13 +9383,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119626854</t>
+          <t>https://artportalen.se/Sighting/119626366</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119627132</v>
+        <v>119626794</v>
       </c>
       <c r="B87" t="n">
         <v>93197</v>
@@ -9404,10 +9424,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>600181</v>
+        <v>600044</v>
       </c>
       <c r="R87" t="n">
-        <v>7063828</v>
+        <v>7063902</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9465,13 +9485,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119627132</t>
+          <t>https://artportalen.se/Sighting/119626794</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119627285</v>
+        <v>119626854</v>
       </c>
       <c r="B88" t="n">
         <v>93197</v>
@@ -9506,10 +9526,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>600141</v>
+        <v>600066</v>
       </c>
       <c r="R88" t="n">
-        <v>7063851</v>
+        <v>7063913</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9567,13 +9587,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119627285</t>
+          <t>https://artportalen.se/Sighting/119626854</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119627439</v>
+        <v>119627132</v>
       </c>
       <c r="B89" t="n">
         <v>93197</v>
@@ -9608,10 +9628,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>600151</v>
+        <v>600181</v>
       </c>
       <c r="R89" t="n">
-        <v>7063852</v>
+        <v>7063828</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9669,13 +9689,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119627439</t>
+          <t>https://artportalen.se/Sighting/119627132</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119698809</v>
+        <v>119627285</v>
       </c>
       <c r="B90" t="n">
         <v>93197</v>
@@ -9710,13 +9730,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>600057</v>
+        <v>600141</v>
       </c>
       <c r="R90" t="n">
-        <v>7064128</v>
+        <v>7063851</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9740,12 +9760,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9771,13 +9791,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119698809</t>
+          <t>https://artportalen.se/Sighting/119627285</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119698843</v>
+        <v>119627439</v>
       </c>
       <c r="B91" t="n">
         <v>93197</v>
@@ -9812,13 +9832,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>600049</v>
+        <v>600151</v>
       </c>
       <c r="R91" t="n">
-        <v>7064094</v>
+        <v>7063852</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9842,12 +9862,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9873,13 +9893,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119698843</t>
+          <t>https://artportalen.se/Sighting/119627439</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119698954</v>
+        <v>119698809</v>
       </c>
       <c r="B92" t="n">
         <v>93197</v>
@@ -9914,10 +9934,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>600048</v>
+        <v>600057</v>
       </c>
       <c r="R92" t="n">
-        <v>7064066</v>
+        <v>7064128</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -9975,13 +9995,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119698954</t>
+          <t>https://artportalen.se/Sighting/119698809</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119699467</v>
+        <v>119698843</v>
       </c>
       <c r="B93" t="n">
         <v>93197</v>
@@ -10016,13 +10036,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>600063</v>
+        <v>600049</v>
       </c>
       <c r="R93" t="n">
-        <v>7064101</v>
+        <v>7064094</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10077,13 +10097,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119699467</t>
+          <t>https://artportalen.se/Sighting/119698843</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119699547</v>
+        <v>119698954</v>
       </c>
       <c r="B94" t="n">
         <v>93197</v>
@@ -10118,13 +10138,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>600083</v>
+        <v>600048</v>
       </c>
       <c r="R94" t="n">
-        <v>7064139</v>
+        <v>7064066</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10179,13 +10199,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119699547</t>
+          <t>https://artportalen.se/Sighting/119698954</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119700486</v>
+        <v>119699467</v>
       </c>
       <c r="B95" t="n">
         <v>93197</v>
@@ -10220,10 +10240,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>600128</v>
+        <v>600063</v>
       </c>
       <c r="R95" t="n">
-        <v>7064081</v>
+        <v>7064101</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10281,13 +10301,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700486</t>
+          <t>https://artportalen.se/Sighting/119699467</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119700514</v>
+        <v>119699547</v>
       </c>
       <c r="B96" t="n">
         <v>93197</v>
@@ -10322,10 +10342,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>600148</v>
+        <v>600083</v>
       </c>
       <c r="R96" t="n">
-        <v>7064068</v>
+        <v>7064139</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10383,13 +10403,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700514</t>
+          <t>https://artportalen.se/Sighting/119699547</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119700543</v>
+        <v>119700486</v>
       </c>
       <c r="B97" t="n">
         <v>93197</v>
@@ -10424,13 +10444,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>600114</v>
+        <v>600128</v>
       </c>
       <c r="R97" t="n">
-        <v>7064069</v>
+        <v>7064081</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10485,13 +10505,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700543</t>
+          <t>https://artportalen.se/Sighting/119700486</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119700694</v>
+        <v>119700514</v>
       </c>
       <c r="B98" t="n">
         <v>93197</v>
@@ -10526,10 +10546,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>600158</v>
+        <v>600148</v>
       </c>
       <c r="R98" t="n">
-        <v>7064002</v>
+        <v>7064068</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10587,13 +10607,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700694</t>
+          <t>https://artportalen.se/Sighting/119700514</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119700839</v>
+        <v>119700543</v>
       </c>
       <c r="B99" t="n">
         <v>93197</v>
@@ -10628,10 +10648,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>600178</v>
+        <v>600114</v>
       </c>
       <c r="R99" t="n">
-        <v>7063985</v>
+        <v>7064069</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10689,13 +10709,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700839</t>
+          <t>https://artportalen.se/Sighting/119700543</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119700878</v>
+        <v>119700694</v>
       </c>
       <c r="B100" t="n">
         <v>93197</v>
@@ -10730,13 +10750,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>600199</v>
+        <v>600158</v>
       </c>
       <c r="R100" t="n">
-        <v>7063963</v>
+        <v>7064002</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10791,16 +10811,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700878</t>
+          <t>https://artportalen.se/Sighting/119700694</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119596575</v>
+        <v>119700839</v>
       </c>
       <c r="B101" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10808,21 +10828,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10832,10 +10852,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>600045</v>
+        <v>600178</v>
       </c>
       <c r="R101" t="n">
-        <v>7064034</v>
+        <v>7063985</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10862,12 +10882,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10893,16 +10913,16 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119596575</t>
+          <t>https://artportalen.se/Sighting/119700839</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119599892</v>
+        <v>119700878</v>
       </c>
       <c r="B102" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10910,21 +10930,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10934,13 +10954,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>600208</v>
+        <v>600199</v>
       </c>
       <c r="R102" t="n">
-        <v>7063973</v>
+        <v>7063963</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10964,12 +10984,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10995,16 +11015,16 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599892</t>
+          <t>https://artportalen.se/Sighting/119700878</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119602111</v>
+        <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93209</v>
+        <v>93416</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11012,37 +11032,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Gärdselet, Gärdselet, Ång</t>
+          <t>Gärdselet, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>599994</v>
+        <v>600114</v>
       </c>
       <c r="R103" t="n">
-        <v>7063980</v>
+        <v>7064155</v>
       </c>
       <c r="S103" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11066,12 +11086,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11097,16 +11117,16 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119602111</t>
+          <t>https://artportalen.se/Sighting/137098779</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119602599</v>
+        <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93209</v>
+        <v>93416</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11114,37 +11134,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Gärdselet, Gärdselet, Ång</t>
+          <t>Gärdselet, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>600009</v>
+        <v>600121</v>
       </c>
       <c r="R104" t="n">
-        <v>7063917</v>
+        <v>7063978</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11168,12 +11188,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11199,13 +11219,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119602599</t>
+          <t>https://artportalen.se/Sighting/137100132</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119603265</v>
+        <v>119596575</v>
       </c>
       <c r="B105" t="n">
         <v>93209</v>
@@ -11240,13 +11260,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>600071</v>
+        <v>600045</v>
       </c>
       <c r="R105" t="n">
-        <v>7063864</v>
+        <v>7064034</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11301,13 +11321,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603265</t>
+          <t>https://artportalen.se/Sighting/119596575</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119603463</v>
+        <v>119599892</v>
       </c>
       <c r="B106" t="n">
         <v>93209</v>
@@ -11342,10 +11362,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>600088</v>
+        <v>600208</v>
       </c>
       <c r="R106" t="n">
-        <v>7063916</v>
+        <v>7063973</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11403,13 +11423,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603463</t>
+          <t>https://artportalen.se/Sighting/119599892</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119626178</v>
+        <v>119602111</v>
       </c>
       <c r="B107" t="n">
         <v>93209</v>
@@ -11444,13 +11464,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>600064</v>
+        <v>599994</v>
       </c>
       <c r="R107" t="n">
-        <v>7063968</v>
+        <v>7063980</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11474,12 +11494,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11505,13 +11525,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119626178</t>
+          <t>https://artportalen.se/Sighting/119602111</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119626895</v>
+        <v>119602599</v>
       </c>
       <c r="B108" t="n">
         <v>93209</v>
@@ -11546,13 +11566,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>600134</v>
+        <v>600009</v>
       </c>
       <c r="R108" t="n">
-        <v>7063899</v>
+        <v>7063917</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11576,12 +11596,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11607,13 +11627,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119626895</t>
+          <t>https://artportalen.se/Sighting/119602599</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119627333</v>
+        <v>119603265</v>
       </c>
       <c r="B109" t="n">
         <v>93209</v>
@@ -11648,13 +11668,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>600132</v>
+        <v>600071</v>
       </c>
       <c r="R109" t="n">
-        <v>7063879</v>
+        <v>7063864</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11678,12 +11698,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11709,13 +11729,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119627333</t>
+          <t>https://artportalen.se/Sighting/119603265</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119627404</v>
+        <v>119603463</v>
       </c>
       <c r="B110" t="n">
         <v>93209</v>
@@ -11750,13 +11770,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>600101</v>
+        <v>600088</v>
       </c>
       <c r="R110" t="n">
-        <v>7063880</v>
+        <v>7063916</v>
       </c>
       <c r="S110" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11780,12 +11800,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11811,13 +11831,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119627404</t>
+          <t>https://artportalen.se/Sighting/119603463</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119627482</v>
+        <v>119626178</v>
       </c>
       <c r="B111" t="n">
         <v>93209</v>
@@ -11852,10 +11872,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>600189</v>
+        <v>600064</v>
       </c>
       <c r="R111" t="n">
-        <v>7063820</v>
+        <v>7063968</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11913,13 +11933,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119627482</t>
+          <t>https://artportalen.se/Sighting/119626178</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119627496</v>
+        <v>119626895</v>
       </c>
       <c r="B112" t="n">
         <v>93209</v>
@@ -11954,10 +11974,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>600198</v>
+        <v>600134</v>
       </c>
       <c r="R112" t="n">
-        <v>7063804</v>
+        <v>7063899</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12015,13 +12035,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119627496</t>
+          <t>https://artportalen.se/Sighting/119626895</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119699994</v>
+        <v>119627333</v>
       </c>
       <c r="B113" t="n">
         <v>93209</v>
@@ -12056,13 +12076,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>600095</v>
+        <v>600132</v>
       </c>
       <c r="R113" t="n">
-        <v>7064182</v>
+        <v>7063879</v>
       </c>
       <c r="S113" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12086,12 +12106,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12117,13 +12137,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119699994</t>
+          <t>https://artportalen.se/Sighting/119627333</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119700909</v>
+        <v>119627404</v>
       </c>
       <c r="B114" t="n">
         <v>93209</v>
@@ -12158,13 +12178,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>600203</v>
+        <v>600101</v>
       </c>
       <c r="R114" t="n">
-        <v>7063934</v>
+        <v>7063880</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12188,12 +12208,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12219,13 +12239,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700909</t>
+          <t>https://artportalen.se/Sighting/119627404</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119700976</v>
+        <v>119627482</v>
       </c>
       <c r="B115" t="n">
         <v>93209</v>
@@ -12260,10 +12280,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>600212</v>
+        <v>600189</v>
       </c>
       <c r="R115" t="n">
-        <v>7063897</v>
+        <v>7063820</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12290,12 +12310,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12321,13 +12341,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700976</t>
+          <t>https://artportalen.se/Sighting/119627482</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119701165</v>
+        <v>119627496</v>
       </c>
       <c r="B116" t="n">
         <v>93209</v>
@@ -12362,13 +12382,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>600230</v>
+        <v>600198</v>
       </c>
       <c r="R116" t="n">
-        <v>7063813</v>
+        <v>7063804</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12392,12 +12412,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12423,16 +12443,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119701165</t>
+          <t>https://artportalen.se/Sighting/119627496</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119596991</v>
+        <v>119699994</v>
       </c>
       <c r="B117" t="n">
-        <v>92841</v>
+        <v>93209</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12440,21 +12460,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12464,10 +12484,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>600056</v>
+        <v>600095</v>
       </c>
       <c r="R117" t="n">
-        <v>7064042</v>
+        <v>7064182</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -12494,12 +12514,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12525,16 +12545,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119596991</t>
+          <t>https://artportalen.se/Sighting/119699994</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119597475</v>
+        <v>119700909</v>
       </c>
       <c r="B118" t="n">
-        <v>92841</v>
+        <v>93209</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12542,21 +12562,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12566,13 +12586,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>600057</v>
+        <v>600203</v>
       </c>
       <c r="R118" t="n">
-        <v>7064055</v>
+        <v>7063934</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12596,12 +12616,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12627,16 +12647,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119597475</t>
+          <t>https://artportalen.se/Sighting/119700909</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119597964</v>
+        <v>119700976</v>
       </c>
       <c r="B119" t="n">
-        <v>92841</v>
+        <v>93209</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12644,21 +12664,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12668,10 +12688,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>600103</v>
+        <v>600212</v>
       </c>
       <c r="R119" t="n">
-        <v>7064111</v>
+        <v>7063897</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12698,12 +12718,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12729,16 +12749,16 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119597964</t>
+          <t>https://artportalen.se/Sighting/119700976</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119598810</v>
+        <v>119701165</v>
       </c>
       <c r="B120" t="n">
-        <v>92841</v>
+        <v>93209</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12746,21 +12766,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12770,13 +12790,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>600084</v>
+        <v>600230</v>
       </c>
       <c r="R120" t="n">
-        <v>7064135</v>
+        <v>7063813</v>
       </c>
       <c r="S120" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12800,12 +12820,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12831,13 +12851,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119598810</t>
+          <t>https://artportalen.se/Sighting/119701165</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119599156</v>
+        <v>119596991</v>
       </c>
       <c r="B121" t="n">
         <v>92841</v>
@@ -12872,13 +12892,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>600090</v>
+        <v>600056</v>
       </c>
       <c r="R121" t="n">
-        <v>7064153</v>
+        <v>7064042</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12933,13 +12953,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599156</t>
+          <t>https://artportalen.se/Sighting/119596991</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119600409</v>
+        <v>119597475</v>
       </c>
       <c r="B122" t="n">
         <v>92841</v>
@@ -12974,10 +12994,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>600282</v>
+        <v>600057</v>
       </c>
       <c r="R122" t="n">
-        <v>7064007</v>
+        <v>7064055</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13035,13 +13055,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119600409</t>
+          <t>https://artportalen.se/Sighting/119597475</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119601484</v>
+        <v>119597964</v>
       </c>
       <c r="B123" t="n">
         <v>92841</v>
@@ -13076,10 +13096,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>600025</v>
+        <v>600103</v>
       </c>
       <c r="R123" t="n">
-        <v>7064036</v>
+        <v>7064111</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13137,13 +13157,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119601484</t>
+          <t>https://artportalen.se/Sighting/119597964</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119601691</v>
+        <v>119598810</v>
       </c>
       <c r="B124" t="n">
         <v>92841</v>
@@ -13178,13 +13198,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>600027</v>
+        <v>600084</v>
       </c>
       <c r="R124" t="n">
-        <v>7063997</v>
+        <v>7064135</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13239,13 +13259,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119601691</t>
+          <t>https://artportalen.se/Sighting/119598810</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119602641</v>
+        <v>119599156</v>
       </c>
       <c r="B125" t="n">
         <v>92841</v>
@@ -13280,10 +13300,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>600018</v>
+        <v>600090</v>
       </c>
       <c r="R125" t="n">
-        <v>7063871</v>
+        <v>7064153</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13341,13 +13361,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119602641</t>
+          <t>https://artportalen.se/Sighting/119599156</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119603015</v>
+        <v>119600409</v>
       </c>
       <c r="B126" t="n">
         <v>92841</v>
@@ -13382,10 +13402,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>600032</v>
+        <v>600282</v>
       </c>
       <c r="R126" t="n">
-        <v>7063852</v>
+        <v>7064007</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13443,13 +13463,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603015</t>
+          <t>https://artportalen.se/Sighting/119600409</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119603682</v>
+        <v>119601484</v>
       </c>
       <c r="B127" t="n">
         <v>92841</v>
@@ -13484,10 +13504,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>600105</v>
+        <v>600025</v>
       </c>
       <c r="R127" t="n">
-        <v>7063827</v>
+        <v>7064036</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13545,38 +13565,38 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603682</t>
+          <t>https://artportalen.se/Sighting/119601484</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119699105</v>
+        <v>119601691</v>
       </c>
       <c r="B128" t="n">
-        <v>90710</v>
+        <v>92841</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6286</v>
+        <v>4745</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13586,13 +13606,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>600061</v>
+        <v>600027</v>
       </c>
       <c r="R128" t="n">
-        <v>7064063</v>
+        <v>7063997</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13616,12 +13636,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13647,38 +13667,38 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119699105</t>
+          <t>https://artportalen.se/Sighting/119601691</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119699302</v>
+        <v>119602641</v>
       </c>
       <c r="B129" t="n">
-        <v>90710</v>
+        <v>92841</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6286</v>
+        <v>4745</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13688,13 +13708,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>600082</v>
+        <v>600018</v>
       </c>
       <c r="R129" t="n">
-        <v>7064058</v>
+        <v>7063871</v>
       </c>
       <c r="S129" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13718,12 +13738,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13749,54 +13769,51 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119699302</t>
+          <t>https://artportalen.se/Sighting/119602641</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119700076</v>
+        <v>119603015</v>
       </c>
       <c r="B130" t="n">
-        <v>90710</v>
+        <v>92841</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6286</v>
+        <v>4745</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Gärdselet, Gärdselet, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>600098</v>
+        <v>600032</v>
       </c>
       <c r="R130" t="n">
-        <v>7064138</v>
+        <v>7063852</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13823,26 +13840,20 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Torrmusseron? Sandtallskog</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF130" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13860,38 +13871,38 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700076</t>
+          <t>https://artportalen.se/Sighting/119603015</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119603316</v>
+        <v>119603682</v>
       </c>
       <c r="B131" t="n">
-        <v>57141</v>
+        <v>92841</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>4745</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13901,13 +13912,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>600073</v>
+        <v>600105</v>
       </c>
       <c r="R131" t="n">
-        <v>7063881</v>
+        <v>7063827</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13937,11 +13948,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13967,16 +13973,16 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119603316</t>
+          <t>https://artportalen.se/Sighting/119603682</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119597299</v>
+        <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>58114</v>
+        <v>93060</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13984,42 +13990,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>103021</v>
+        <v>4745</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gärdselet, Gärdselet, Ång</t>
+          <t>Gärdselet, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>600066</v>
+        <v>600072</v>
       </c>
       <c r="R132" t="n">
-        <v>7064056</v>
+        <v>7064053</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14043,12 +14044,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14074,56 +14075,51 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119597299</t>
+          <t>https://artportalen.se/Sighting/137100370</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119599666</v>
+        <v>119699105</v>
       </c>
       <c r="B133" t="n">
-        <v>58114</v>
+        <v>90710</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Gärdselet, Gärdselet, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>600161</v>
+        <v>600061</v>
       </c>
       <c r="R133" t="n">
-        <v>7064046</v>
+        <v>7064063</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14150,12 +14146,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14181,59 +14177,54 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119599666</t>
+          <t>https://artportalen.se/Sighting/119699105</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119698974</v>
+        <v>119699302</v>
       </c>
       <c r="B134" t="n">
-        <v>58114</v>
+        <v>90710</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Gärdselet, Gärdselet, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>600067</v>
+        <v>600082</v>
       </c>
       <c r="R134" t="n">
-        <v>7064072</v>
+        <v>7064058</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14288,59 +14279,57 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119698974</t>
+          <t>https://artportalen.se/Sighting/119699302</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119699915</v>
+        <v>119700076</v>
       </c>
       <c r="B135" t="n">
-        <v>58114</v>
+        <v>90710</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Gärdselet, Gärdselet, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>600096</v>
+        <v>600098</v>
       </c>
       <c r="R135" t="n">
-        <v>7064168</v>
+        <v>7064138</v>
       </c>
       <c r="S135" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14372,12 +14361,18 @@
           <t>2024-09-12</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Torrmusseron? Sandtallskog</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14395,59 +14390,54 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119699915</t>
+          <t>https://artportalen.se/Sighting/119700076</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119700921</v>
+        <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>58114</v>
+        <v>90900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Gärdselet, Gärdselet, Ång</t>
+          <t>Gärdselet, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>600216</v>
+        <v>600105</v>
       </c>
       <c r="R136" t="n">
-        <v>7063935</v>
+        <v>7064081</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14471,12 +14461,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14502,16 +14492,16 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119700921</t>
+          <t>https://artportalen.se/Sighting/137098719</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119601370</v>
+        <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>91605</v>
+        <v>90900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14519,35 +14509,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>233195</v>
+        <v>6286</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramaria neoformosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>sensu Schild</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gärdselet, Gärdselet, Ång</t>
+          <t>Gärdselet, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>600046</v>
+        <v>600077</v>
       </c>
       <c r="R137" t="n">
-        <v>7064025</v>
+        <v>7064138</v>
       </c>
       <c r="S137" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14571,26 +14563,20 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Ramaria neoformosa? Sandtallskog</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
       <c r="AE137" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF137" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -14607,6 +14593,1191 @@
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137099430</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137099721</v>
+      </c>
+      <c r="B138" t="n">
+        <v>90900</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>600119</v>
+      </c>
+      <c r="R138" t="n">
+        <v>7063831</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137099721</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137099942</v>
+      </c>
+      <c r="B139" t="n">
+        <v>90900</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>600088</v>
+      </c>
+      <c r="R139" t="n">
+        <v>7063906</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137099942</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>137100089</v>
+      </c>
+      <c r="B140" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Löningsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>600230</v>
+      </c>
+      <c r="R140" t="n">
+        <v>7063849</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137100089</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>119603316</v>
+      </c>
+      <c r="B141" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>600073</v>
+      </c>
+      <c r="R141" t="n">
+        <v>7063881</v>
+      </c>
+      <c r="S141" t="n">
+        <v>15</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603316</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>119597299</v>
+      </c>
+      <c r="B142" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>600066</v>
+      </c>
+      <c r="R142" t="n">
+        <v>7064056</v>
+      </c>
+      <c r="S142" t="n">
+        <v>25</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119597299</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>119599666</v>
+      </c>
+      <c r="B143" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>600161</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7064046</v>
+      </c>
+      <c r="S143" t="n">
+        <v>15</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599666</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>119698974</v>
+      </c>
+      <c r="B144" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>600067</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7064072</v>
+      </c>
+      <c r="S144" t="n">
+        <v>25</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119698974</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>119699915</v>
+      </c>
+      <c r="B145" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>600096</v>
+      </c>
+      <c r="R145" t="n">
+        <v>7064168</v>
+      </c>
+      <c r="S145" t="n">
+        <v>25</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699915</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>119700921</v>
+      </c>
+      <c r="B146" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>600216</v>
+      </c>
+      <c r="R146" t="n">
+        <v>7063935</v>
+      </c>
+      <c r="S146" t="n">
+        <v>25</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119700921</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>137098574</v>
+      </c>
+      <c r="B147" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>600077</v>
+      </c>
+      <c r="R147" t="n">
+        <v>7064064</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137098574</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>119601370</v>
+      </c>
+      <c r="B148" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>233195</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Ramaria neoformosa</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>sensu Schild</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>600046</v>
+      </c>
+      <c r="R148" t="n">
+        <v>7064025</v>
+      </c>
+      <c r="S148" t="n">
+        <v>20</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Ramaria neoformosa? Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119601370</t>
         </is>
@@ -14750,6 +15921,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>137100089</v>
       </c>
       <c r="B140" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>137100089</v>
       </c>
       <c r="B140" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>137100089</v>
       </c>
       <c r="B140" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>137098574</v>
       </c>
       <c r="B147" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>137100089</v>
       </c>
       <c r="B140" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>137098574</v>
       </c>
       <c r="B147" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -15591,11 +15591,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Gärdselet, Ång</t>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ148"/>
+  <dimension ref="A1:AZ155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>119601370</v>
       </c>
       <c r="B148" t="n">
-        <v>91605</v>
+        <v>91646</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15748,14 +15748,14 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ramaria neoformosa? Sandtallskog</t>
+          <t>Osäker artbestämning. Sandtallskog</t>
         </is>
       </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
@@ -15776,6 +15776,783 @@
       <c r="AZ148" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119601370</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>119596675</v>
+      </c>
+      <c r="B149" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>600070</v>
+      </c>
+      <c r="R149" t="n">
+        <v>7064032</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119596675</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>119598070</v>
+      </c>
+      <c r="B150" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>600103</v>
+      </c>
+      <c r="R150" t="n">
+        <v>7064111</v>
+      </c>
+      <c r="S150" t="n">
+        <v>20</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119598070</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>119604292</v>
+      </c>
+      <c r="B151" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>600165</v>
+      </c>
+      <c r="R151" t="n">
+        <v>7063791</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119604292</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>119698837</v>
+      </c>
+      <c r="B152" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>600052</v>
+      </c>
+      <c r="R152" t="n">
+        <v>7064115</v>
+      </c>
+      <c r="S152" t="n">
+        <v>15</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119698837</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>119699372</v>
+      </c>
+      <c r="B153" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>600070</v>
+      </c>
+      <c r="R153" t="n">
+        <v>7064055</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699372</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>119699449</v>
+      </c>
+      <c r="B154" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>600076</v>
+      </c>
+      <c r="R154" t="n">
+        <v>7064069</v>
+      </c>
+      <c r="S154" t="n">
+        <v>15</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699449</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>119700450</v>
+      </c>
+      <c r="B155" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Gärdselet, Gärdselet, Ång</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>600100</v>
+      </c>
+      <c r="R155" t="n">
+        <v>7064106</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119700450</t>
         </is>
       </c>
     </row>
@@ -15928,6 +16705,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>137100089</v>
       </c>
       <c r="B140" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>137098574</v>
       </c>
       <c r="B147" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>119601370</v>
       </c>
       <c r="B148" t="n">
-        <v>91646</v>
+        <v>91656</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>119596675</v>
       </c>
       <c r="B149" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>119598070</v>
       </c>
       <c r="B150" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>119604292</v>
       </c>
       <c r="B151" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>119698837</v>
       </c>
       <c r="B152" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>119699372</v>
       </c>
       <c r="B153" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>119699449</v>
       </c>
       <c r="B154" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>119700450</v>
       </c>
       <c r="B155" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>119601370</v>
       </c>
       <c r="B148" t="n">
-        <v>91656</v>
+        <v>91657</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>119596675</v>
       </c>
       <c r="B149" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>119598070</v>
       </c>
       <c r="B150" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>119604292</v>
       </c>
       <c r="B151" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>119698837</v>
       </c>
       <c r="B152" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>119699372</v>
       </c>
       <c r="B153" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>119699449</v>
       </c>
       <c r="B154" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>119700450</v>
       </c>
       <c r="B155" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93101</v>
+        <v>93104</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>137100089</v>
       </c>
       <c r="B140" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>137098574</v>
       </c>
       <c r="B147" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>119601370</v>
       </c>
       <c r="B148" t="n">
-        <v>91657</v>
+        <v>91660</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>119596675</v>
       </c>
       <c r="B149" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>119598070</v>
       </c>
       <c r="B150" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>119604292</v>
       </c>
       <c r="B151" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>119698837</v>
       </c>
       <c r="B152" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>119699372</v>
       </c>
       <c r="B153" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>119699449</v>
       </c>
       <c r="B154" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>119700450</v>
       </c>
       <c r="B155" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93104</v>
+        <v>93106</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>119601370</v>
       </c>
       <c r="B148" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>119596675</v>
       </c>
       <c r="B149" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>119598070</v>
       </c>
       <c r="B150" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>119604292</v>
       </c>
       <c r="B151" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>119698837</v>
       </c>
       <c r="B152" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>119699372</v>
       </c>
       <c r="B153" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>119699449</v>
       </c>
       <c r="B154" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>119700450</v>
       </c>
       <c r="B155" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93106</v>
+        <v>93112</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>137100089</v>
       </c>
       <c r="B140" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>137098574</v>
       </c>
       <c r="B147" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>119601370</v>
       </c>
       <c r="B148" t="n">
-        <v>91662</v>
+        <v>91667</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>119596675</v>
       </c>
       <c r="B149" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>119598070</v>
       </c>
       <c r="B150" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>119604292</v>
       </c>
       <c r="B151" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>119698837</v>
       </c>
       <c r="B152" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>119699372</v>
       </c>
       <c r="B153" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>119699449</v>
       </c>
       <c r="B154" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>119700450</v>
       </c>
       <c r="B155" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>137100089</v>
       </c>
       <c r="B140" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>119601370</v>
       </c>
       <c r="B148" t="n">
-        <v>91667</v>
+        <v>91679</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>119596675</v>
       </c>
       <c r="B149" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>119598070</v>
       </c>
       <c r="B150" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>119604292</v>
       </c>
       <c r="B151" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>119698837</v>
       </c>
       <c r="B152" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>119699372</v>
       </c>
       <c r="B153" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>119699449</v>
       </c>
       <c r="B154" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>119700450</v>
       </c>
       <c r="B155" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>137100089</v>
       </c>
       <c r="B140" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>119601370</v>
       </c>
       <c r="B148" t="n">
-        <v>91679</v>
+        <v>91680</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>119596675</v>
       </c>
       <c r="B149" t="n">
-        <v>91655</v>
+        <v>91656</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>119598070</v>
       </c>
       <c r="B150" t="n">
-        <v>91655</v>
+        <v>91656</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>119604292</v>
       </c>
       <c r="B151" t="n">
-        <v>91655</v>
+        <v>91656</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>119698837</v>
       </c>
       <c r="B152" t="n">
-        <v>91655</v>
+        <v>91656</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>119699372</v>
       </c>
       <c r="B153" t="n">
-        <v>91655</v>
+        <v>91656</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>119699449</v>
       </c>
       <c r="B154" t="n">
-        <v>91655</v>
+        <v>91656</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>119700450</v>
       </c>
       <c r="B155" t="n">
-        <v>91655</v>
+        <v>91656</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>137100089</v>
       </c>
       <c r="B140" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>119601370</v>
       </c>
       <c r="B148" t="n">
-        <v>91680</v>
+        <v>91683</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>119596675</v>
       </c>
       <c r="B149" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>119598070</v>
       </c>
       <c r="B150" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>119604292</v>
       </c>
       <c r="B151" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>119698837</v>
       </c>
       <c r="B152" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>119699372</v>
       </c>
       <c r="B153" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>119699449</v>
       </c>
       <c r="B154" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>119700450</v>
       </c>
       <c r="B155" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/A 39526-2026 artfynd.xlsx
+++ b/artfynd/A 39526-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137099440</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137099819</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>137098779</v>
       </c>
       <c r="B103" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>137100132</v>
       </c>
       <c r="B104" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>137100370</v>
       </c>
       <c r="B132" t="n">
-        <v>93128</v>
+        <v>93132</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>137098719</v>
       </c>
       <c r="B136" t="n">
-        <v>90967</v>
+        <v>90971</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>137099430</v>
       </c>
       <c r="B137" t="n">
-        <v>90967</v>
+        <v>90971</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>137099721</v>
       </c>
       <c r="B138" t="n">
-        <v>90967</v>
+        <v>90971</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>137099942</v>
       </c>
       <c r="B139" t="n">
-        <v>90967</v>
+        <v>90971</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>137100089</v>
       </c>
       <c r="B140" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>137098574</v>
       </c>
       <c r="B147" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>119601370</v>
       </c>
       <c r="B148" t="n">
-        <v>91683</v>
+        <v>91687</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>119596675</v>
       </c>
       <c r="B149" t="n">
-        <v>91659</v>
+        <v>91663</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>119598070</v>
       </c>
       <c r="B150" t="n">
-        <v>91659</v>
+        <v>91663</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>119604292</v>
       </c>
       <c r="B151" t="n">
-        <v>91659</v>
+        <v>91663</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>119698837</v>
       </c>
       <c r="B152" t="n">
-        <v>91659</v>
+        <v>91663</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>119699372</v>
       </c>
       <c r="B153" t="n">
-        <v>91659</v>
+        <v>91663</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>119699449</v>
       </c>
       <c r="B154" t="n">
-        <v>91659</v>
+        <v>91663</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>119700450</v>
       </c>
       <c r="B155" t="n">
-        <v>91659</v>
+        <v>91663</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
